--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486429_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486429_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6352</v>
+        <v>4.0755</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2532</v>
+        <v>1.5394</v>
       </c>
       <c r="F2" t="n">
-        <v>2.382</v>
+        <v>2.5361</v>
       </c>
       <c r="G2" t="n">
         <v>2.1516</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9403</v>
+        <v>0.3806</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1032</v>
+        <v>0.3894</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1628</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.0207</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5362</v>
+        <v>2.2645</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7799</v>
+        <v>1.607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7563</v>
+        <v>0.6575</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.8932</v>
+        <v>1.4334</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6962</v>
+        <v>1.5418</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.197</v>
+        <v>-0.1084</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.9082</v>
+        <v>1.73</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7694</v>
+        <v>1.0981</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.1387</v>
+        <v>0.6319</v>
       </c>
       <c r="M3" t="n">
-        <v>0.015</v>
+        <v>-0.2966</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0732</v>
+        <v>0.4437</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0583</v>
+        <v>-0.7403</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3015</v>
+        <v>-0.2989</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3003</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9987</v>
+        <v>-0.3086</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4753</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>5.4753</v>
+        <v>2.2599</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8083</v>
+        <v>1.8883</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4383</v>
+        <v>0.3951</v>
       </c>
       <c r="F4" t="n">
-        <v>1.37</v>
+        <v>1.4933</v>
       </c>
       <c r="G4" t="n">
         <v>2.4211</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0822</v>
+        <v>0.1622</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2896</v>
+        <v>0.2464</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2074</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6796</v>
+        <v>1.8763</v>
       </c>
       <c r="E5" t="n">
-        <v>0.868</v>
+        <v>0.8426</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8116</v>
+        <v>1.0337</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4334</v>
+        <v>-3.8932</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5418</v>
+        <v>-0.6962</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1084</v>
+        <v>-3.197</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>-3.9082</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0981</v>
+        <v>-1.7694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6319</v>
+        <v>-2.1387</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2966</v>
+        <v>0.015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4437</v>
+        <v>1.0732</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7403</v>
+        <v>-1.0583</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8839</v>
+        <v>-0.3584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7294</v>
+        <v>0.3629</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1544</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>5.4753</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2599</v>
+        <v>5.4753</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5241</v>
+        <v>1.7591</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9992</v>
+        <v>2.111</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4751</v>
+        <v>-0.3518</v>
       </c>
       <c r="G6" t="n">
         <v>2.0259</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9368</v>
+        <v>-0.7018</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4675</v>
+        <v>-0.3557</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4694</v>
+        <v>-0.3461</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1103</v>
+        <v>1.3163</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1993</v>
+        <v>0.7701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.911</v>
+        <v>0.5462</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5384</v>
+        <v>0.9225</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3958</v>
+        <v>-1.7151</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8574000000000001</v>
+        <v>2.6376</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6787</v>
+        <v>1.27</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6022</v>
+        <v>-2.1923</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>3.4624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1403</v>
+        <v>-0.3476</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7936</v>
+        <v>0.4772</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9339</v>
+        <v>-0.8248</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0806</v>
+        <v>-1.1287</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>-0.4999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3988</v>
+        <v>-0.6288</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5782</v>
+        <v>0.9515</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1861</v>
+        <v>0.3795</v>
       </c>
       <c r="F8" t="n">
-        <v>0.392</v>
+        <v>0.572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9225</v>
+        <v>0.5384</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7151</v>
+        <v>1.3958</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6376</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.27</v>
+        <v>0.6787</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1923</v>
+        <v>0.6022</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4624</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3476</v>
+        <v>-0.1403</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4772</v>
+        <v>0.7936</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8248</v>
+        <v>-0.9339</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8668</v>
+        <v>-0.2394</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0839</v>
+        <v>-0.2992</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7829</v>
+        <v>0.0598</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4689</v>
+        <v>0.623</v>
       </c>
       <c r="E9" t="n">
         <v>0.3898</v>
       </c>
       <c r="F9" t="n">
-        <v>0.079</v>
+        <v>0.2332</v>
       </c>
       <c r="G9" t="n">
         <v>0.3166</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4572</v>
+        <v>-0.3031</v>
       </c>
       <c r="T9" t="n">
         <v>0.2211</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6784</v>
+        <v>-0.5242</v>
       </c>
       <c r="V9" t="n">
         <v>0.1745</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9265</v>
+        <v>-0.8079</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5216</v>
+        <v>-2.3413</v>
       </c>
       <c r="F10" t="n">
-        <v>1.595</v>
+        <v>1.5334</v>
       </c>
       <c r="G10" t="n">
         <v>0.4659</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2826</v>
+        <v>-0.164</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>-0.2187</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1163</v>
+        <v>0.0547</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2256</v>
+        <v>-1.292</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2294</v>
+        <v>-2.0491</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0037</v>
+        <v>0.7572</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0696</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.591</v>
+        <v>-0.6573</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4927</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0819</v>
+        <v>-0.1646</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.707</v>
+        <v>-1.5498</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0768</v>
+        <v>-2.673</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3699</v>
+        <v>1.1233</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3188</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2555</v>
+        <v>-1.0984</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0839</v>
+        <v>-0.6801</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1716</v>
+        <v>-0.4182</v>
       </c>
       <c r="V12" t="n">
         <v>3.3899</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8281</v>
+        <v>-1.7665</v>
       </c>
       <c r="E13" t="n">
         <v>-1.2245</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6036</v>
+        <v>-0.5419</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3004</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2449</v>
+        <v>-0.1833</v>
       </c>
       <c r="T13" t="n">
         <v>-0.137</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.653599999999997</v>
+        <v>9.3383</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9384999999999981</v>
+        <v>-0.253400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>9.591799999999999</v>
+        <v>9.5922</v>
       </c>
       <c r="G14" t="n">
         <v>2.693399999999999</v>
@@ -1531,7 +1531,7 @@
         <v>-0.2164999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5092</v>
+        <v>7.509199999999998</v>
       </c>
       <c r="O14" t="n">
         <v>-7.7259</v>
@@ -1546,13 +1546,13 @@
         <v>15.2256</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.275300000000001</v>
+        <v>-4.5905</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1389</v>
+        <v>-1.4539</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.1365</v>
+        <v>-3.136400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>9.0604</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6246</v>
+        <v>4.5836</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7783</v>
+        <v>2.6786</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1536</v>
+        <v>1.905</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6604</v>
+        <v>2.2086</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3624</v>
+        <v>4.0875</v>
       </c>
       <c r="I15" t="n">
-        <v>0.298</v>
+        <v>-1.879</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6821</v>
+        <v>1.8072</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5147</v>
+        <v>3.5618</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1674</v>
+        <v>-1.7546</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0217</v>
+        <v>0.4014</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1523</v>
+        <v>0.5258</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>-0.1243</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1902</v>
+        <v>0.5134</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.3064</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7759</v>
+        <v>0.207</v>
       </c>
       <c r="V15" t="n">
-        <v>0.904</v>
+        <v>0.339</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>-0.226</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1899</v>
+        <v>3.8763</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8963</v>
+        <v>4.3312</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2936</v>
+        <v>-0.4549</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2086</v>
+        <v>1.6604</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0875</v>
+        <v>1.3624</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.879</v>
+        <v>0.298</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8072</v>
+        <v>2.6821</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5618</v>
+        <v>1.5147</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.7546</v>
+        <v>1.1674</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4014</v>
+        <v>-1.0217</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5258</v>
+        <v>-0.1523</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1243</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8802</v>
+        <v>0.4419</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>0.5191</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4044</v>
+        <v>-0.0772</v>
       </c>
       <c r="V16" t="n">
-        <v>0.339</v>
+        <v>0.904</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>-0.226</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8612</v>
+        <v>3.4316</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1123</v>
+        <v>4.5594</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2511</v>
+        <v>-1.1278</v>
       </c>
       <c r="G17" t="n">
         <v>5.178</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3528</v>
+        <v>0.2175</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>0.0481</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0461</v>
+        <v>0.1694</v>
       </c>
       <c r="V17" t="n">
         <v>-1.7464</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5713</v>
+        <v>0.7994</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2051</v>
+        <v>0.8698</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3662</v>
+        <v>-0.0704</v>
       </c>
       <c r="G18" t="n">
         <v>0.6561</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1836</v>
+        <v>1.4117</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.6309</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2174</v>
+        <v>0.7808</v>
       </c>
       <c r="V18" t="n">
         <v>-1.921</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.694</v>
+        <v>-0.2101</v>
       </c>
       <c r="E19" t="n">
         <v>-3.7432</v>
       </c>
       <c r="F19" t="n">
-        <v>4.4372</v>
+        <v>3.5331</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4105</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4095</v>
+        <v>1.5054</v>
       </c>
       <c r="T19" t="n">
         <v>0.2007</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2088</v>
+        <v>1.3047</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.616</v>
+        <v>-0.914</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0361</v>
+        <v>-2.4832</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4202</v>
+        <v>1.5692</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8581</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2846</v>
+        <v>0.9866</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6802</v>
+        <v>0.2331</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6044</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2964</v>
+        <v>-2.7756</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6589</v>
+        <v>-2.8759</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6375</v>
+        <v>0.1003</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8118</v>
+        <v>-2.0533</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1416</v>
+        <v>-1.1313</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6702</v>
+        <v>-0.922</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7925</v>
+        <v>-1.8484</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.9072</v>
+        <v>-1.1799</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>-0.6686</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0193</v>
+        <v>-0.2049</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2344</v>
+        <v>0.0486</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7849</v>
+        <v>-0.2534</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5807</v>
+        <v>0.6252</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0911</v>
+        <v>0.0601</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5105</v>
+        <v>0.5651</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7621</v>
+        <v>-3.4955</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3229</v>
+        <v>-2.2177</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4392</v>
+        <v>-1.2778</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0533</v>
+        <v>-3.8118</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1313</v>
+        <v>-3.1416</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.922</v>
+        <v>-0.6702</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8484</v>
+        <v>-2.7925</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1799</v>
+        <v>-2.9072</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6686</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2049</v>
+        <v>-1.0193</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0486</v>
+        <v>-0.2344</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2534</v>
+        <v>-0.7849</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3613</v>
+        <v>0.3815</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3869</v>
+        <v>0.5324</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0256</v>
+        <v>-0.1508</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9008</v>
+        <v>-3.6064</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2524</v>
+        <v>-3.635</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6484</v>
+        <v>0.0286</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2054</v>
+        <v>-2.6388</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5597</v>
+        <v>-2.3448</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7651</v>
+        <v>-0.294</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4311</v>
+        <v>-1.5885</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5229</v>
+        <v>-2.1439</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9539</v>
+        <v>0.5554</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2257</v>
+        <v>-1.0504</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0368</v>
+        <v>-0.2009</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1889</v>
+        <v>-0.8495</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.2626</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4472</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4062</v>
+        <v>0.1286</v>
       </c>
       <c r="U23" t="n">
-        <v>0.041</v>
+        <v>-0.0532</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2907</v>
+        <v>-0.3904</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5512</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2333</v>
+        <v>-3.6735</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.082</v>
+        <v>-3.3642</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1513</v>
+        <v>-0.3093</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6388</v>
+        <v>1.2054</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3448</v>
+        <v>-0.5597</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.294</v>
+        <v>1.7651</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5885</v>
+        <v>1.4311</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.1439</v>
+        <v>-0.5229</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5554</v>
+        <v>1.9539</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0504</v>
+        <v>-0.2257</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2009</v>
+        <v>-0.0368</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8495</v>
+        <v>-0.1889</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6525</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5515</v>
+        <v>0.6745</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3184</v>
+        <v>0.2944</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.233</v>
+        <v>0.38</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3904</v>
+        <v>-2.2907</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3904</v>
+        <v>-1.5512</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.786</v>
+        <v>-4.4341</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4882</v>
+        <v>-3.7117</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2978</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8293</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3255</v>
+        <v>0.6775</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4062</v>
+        <v>0.1827</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0806</v>
+        <v>0.4948</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0647</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.653599999999999</v>
+        <v>-6.4183</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.591699999999999</v>
+        <v>-9.591900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9383000000000004</v>
+        <v>3.173699999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-2.6933</v>
@@ -2482,13 +2482,13 @@
         <v>13.0502</v>
       </c>
       <c r="S26" t="n">
-        <v>5.275499999999999</v>
+        <v>7.5106</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1366</v>
+        <v>3.1365</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1389</v>
+        <v>4.374099999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-9.060399999999998</v>
